--- a/Questions - Round 9.xlsx
+++ b/Questions - Round 9.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stockmeier.sharepoint.com/sites/YoungProfessionalsSTOCKMEIER-YPIII-SustainabilityAwarenessSessions/Freigegebene Dokumente/02. Content/Questions in template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_206634DD33DDCF600C89B91E2ED782A5FDF17E42" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF517AE7-F2AD-4800-B540-6E978273BC03}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_206634DD33DDCF600C89B91E2ED782A5FDF17E42" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C62009C6-0BCB-44A5-9B51-D0C3A44BC22E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="461">
   <si>
     <t>type</t>
   </si>
@@ -1364,6 +1364,58 @@
   </si>
   <si>
     <t>Il dosaggio corretto riduce il carico chimico non necessario e i rifiuti. Le abitudini personali contano, perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Comment E.A</t>
+  </si>
+  <si>
+    <t>Ich würde sagen, dass es hier um das Wasser-SDG geht.
+Wir haben viele wassergefährdende Stoffe, für die gesetzlich vorgeschriebene Sicherheitsmaßnahmen erforderlich sind.</t>
+  </si>
+  <si>
+    <t>Ich würde sagen, dass es hier um Wasser geht.</t>
+  </si>
+  <si>
+    <t>I would say that this is about the water-related SDG.
+We handle many substances hazardous to water that require legally mandated safety measures.</t>
+  </si>
+  <si>
+    <t>I would say that this is about water.</t>
+  </si>
+  <si>
+    <t>Ik zou zeggen dat dit over de watergerelateerde SDG gaat.
+We werken met veel waterverontreinigende stoffen waarvoor wettelijk voorgeschreven veiligheidsmaatregelen vereist zijn.</t>
+  </si>
+  <si>
+    <t>Ik zou zeggen dat dit over water gaat.</t>
+  </si>
+  <si>
+    <t>Je dirais qu’il s’agit ici de l’ODD relatif à l’eau.
+Nous manipulons de nombreuses substances dangereuses pour l’eau qui nécessitent des mesures de sécurité imposées par la loi.</t>
+  </si>
+  <si>
+    <t>Je dirais qu’il s’agit ici de l’eau.</t>
+  </si>
+  <si>
+    <t>Diría que se trata del ODS relacionado con el agua.
+Trabajamos con muchas sustancias peligrosas para el agua que requieren medidas de seguridad establecidas por ley.</t>
+  </si>
+  <si>
+    <t>Diría que se trata del agua.</t>
+  </si>
+  <si>
+    <t>Direi che si tratta dell’OSS relativo all’acqua.
+Gestiamo molte sostanze pericolose per l’acqua che richiedono misure di sicurezza previste dalla legge.</t>
+  </si>
+  <si>
+    <t>Direi che si tratta dell’acqua.</t>
+  </si>
+  <si>
+    <t>Powiedziałbym, że chodzi tu o cel zrównoważonego rozwoju związany z wodą.
+Mamy do czynienia z wieloma substancjami niebezpiecznymi dla wody, które wymagają prawnie określonych środków bezpieczeństwa.</t>
+  </si>
+  <si>
+    <t>Powiedziałbym, że chodzi tu o wodę.</t>
   </si>
 </sst>
 </file>
@@ -1383,16 +1435,19 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1425,7 +1480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1442,11 +1497,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="79">
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -1699,9 +1760,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:J11">
-  <autoFilter ref="A1:J11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Questions" displayName="Questions" ref="A1:K11">
+  <autoFilter ref="A1:K11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="question"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="note"/>
@@ -1712,120 +1773,121 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
+    <tableColumn id="11" xr3:uid="{DED4BCE8-D413-47F6-AA0A-AEC1F9DC6252}" name="Comment E.A" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7F37DD8-4A96-4BC5-A3E9-CEF7521473B6}" name="Questions3" displayName="Questions3" ref="A1:J11" headerRowDxfId="67" dataDxfId="65" totalsRowDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7F37DD8-4A96-4BC5-A3E9-CEF7521473B6}" name="Questions3" displayName="Questions3" ref="A1:J11" headerRowDxfId="65" dataDxfId="64" totalsRowDxfId="63">
   <autoFilter ref="A1:J11" xr:uid="{F7F37DD8-4A96-4BC5-A3E9-CEF7521473B6}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{937C657A-6A54-46B2-BCCA-126FE453E15E}" name="type" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{BF516B13-26F5-4A7B-80B3-4213E7775BC4}" name="question" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{2DF00B78-2A45-4A68-9E56-940A0DC21891}" name="note" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{38D63777-41F7-42CF-89AC-8216A048B425}" name="option1" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{A9934298-B505-4765-89E8-E766763D4394}" name="option2" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{17112123-5BAA-4FF1-A028-6421D92A0ACE}" name="option3" dataDxfId="72"/>
-    <tableColumn id="7" xr3:uid="{3CB5E33E-D8A2-4A08-AF8A-05336F076501}" name="option4" dataDxfId="71"/>
-    <tableColumn id="8" xr3:uid="{B6C6AC47-E994-4620-B5C1-12268B490558}" name="correct" dataDxfId="70"/>
-    <tableColumn id="9" xr3:uid="{847855D7-B914-4DEC-BCD2-29CFA8D4A85B}" name="explanation" dataDxfId="69"/>
-    <tableColumn id="10" xr3:uid="{863A6380-46B7-4250-8D8A-DDAB460C911D}" name="Comments ZF" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{937C657A-6A54-46B2-BCCA-126FE453E15E}" name="type" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{BF516B13-26F5-4A7B-80B3-4213E7775BC4}" name="question" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{2DF00B78-2A45-4A68-9E56-940A0DC21891}" name="note" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{38D63777-41F7-42CF-89AC-8216A048B425}" name="option1" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{A9934298-B505-4765-89E8-E766763D4394}" name="option2" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{17112123-5BAA-4FF1-A028-6421D92A0ACE}" name="option3" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{3CB5E33E-D8A2-4A08-AF8A-05336F076501}" name="option4" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{B6C6AC47-E994-4620-B5C1-12268B490558}" name="correct" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{847855D7-B914-4DEC-BCD2-29CFA8D4A85B}" name="explanation" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{863A6380-46B7-4250-8D8A-DDAB460C911D}" name="Comments ZF" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D156DE85-96DD-496B-9F3B-99CF3FD0E8F0}" name="Questions4" displayName="Questions4" ref="A1:J11" headerRowDxfId="54" dataDxfId="52" totalsRowDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D156DE85-96DD-496B-9F3B-99CF3FD0E8F0}" name="Questions4" displayName="Questions4" ref="A1:J11" headerRowDxfId="52" dataDxfId="51" totalsRowDxfId="50">
   <autoFilter ref="A1:J11" xr:uid="{D156DE85-96DD-496B-9F3B-99CF3FD0E8F0}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{20A2D6A0-E65E-4992-8B9B-5B87D27F1250}" name="type" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{3F2148CB-5CEB-43C3-B7BF-AE472D6BA083}" name="question" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{57E61648-EFEA-4401-BF87-D7DFE7D17709}" name="note" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{E249F9C4-119C-445E-8054-F4B1DB7D148E}" name="option1" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{74D16973-3BAA-4425-83B5-9AE3005C474D}" name="option2" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{A5B559C5-DAB8-4D08-83D5-4104BC20EA18}" name="option3" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{75E575A9-C594-4C3D-B099-3E53129B241D}" name="option4" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{3F98FCC5-3566-4439-BCB2-6E858C76CF1F}" name="correct" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{0476367E-BF0F-4DBD-BEB4-5FB76444200D}" name="explanation" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{4B823691-F3FB-45C3-BDFA-A232A1AA3A13}" name="Comments ZF" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{20A2D6A0-E65E-4992-8B9B-5B87D27F1250}" name="type" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{3F2148CB-5CEB-43C3-B7BF-AE472D6BA083}" name="question" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{57E61648-EFEA-4401-BF87-D7DFE7D17709}" name="note" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{E249F9C4-119C-445E-8054-F4B1DB7D148E}" name="option1" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{74D16973-3BAA-4425-83B5-9AE3005C474D}" name="option2" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{A5B559C5-DAB8-4D08-83D5-4104BC20EA18}" name="option3" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{75E575A9-C594-4C3D-B099-3E53129B241D}" name="option4" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{3F98FCC5-3566-4439-BCB2-6E858C76CF1F}" name="correct" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{0476367E-BF0F-4DBD-BEB4-5FB76444200D}" name="explanation" dataDxfId="41"/>
+    <tableColumn id="10" xr3:uid="{4B823691-F3FB-45C3-BDFA-A232A1AA3A13}" name="Comments ZF" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{441DEC90-8320-4943-B0D2-7B9084164BAF}" name="Questions5" displayName="Questions5" ref="A1:J11" headerRowDxfId="41" dataDxfId="39" totalsRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{441DEC90-8320-4943-B0D2-7B9084164BAF}" name="Questions5" displayName="Questions5" ref="A1:J11" headerRowDxfId="78" dataDxfId="77" totalsRowDxfId="76">
   <autoFilter ref="A1:J11" xr:uid="{441DEC90-8320-4943-B0D2-7B9084164BAF}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A097439A-B3D0-41E1-8DF5-C8B6FCDD22C7}" name="type" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{3767DB65-4071-4A9D-9CEC-E90234B759B8}" name="question" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{A49EBD76-4A4E-42FF-86F4-BD4F97AFF9DA}" name="note" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{650A8E48-D9D9-4FF9-B372-65D8261CF07D}" name="option1" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{3E44332A-5E26-48D0-90BB-9F9039DE9849}" name="option2" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{A3F2BD9D-835E-492D-AF60-1777FDBFC4A3}" name="option3" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{2B52C26E-7952-4BDC-BA0C-415990928F70}" name="option4" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{6B8845CA-AD71-4B12-BE16-31F17CE35C2B}" name="correct" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{81BCF052-D165-4872-A5EE-1654D4C54DA4}" name="explanation" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{AC8E2E79-B61E-4526-B873-A7FAFED87C57}" name="Comments ZF" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{A097439A-B3D0-41E1-8DF5-C8B6FCDD22C7}" name="type" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{3767DB65-4071-4A9D-9CEC-E90234B759B8}" name="question" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{A49EBD76-4A4E-42FF-86F4-BD4F97AFF9DA}" name="note" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{650A8E48-D9D9-4FF9-B372-65D8261CF07D}" name="option1" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{3E44332A-5E26-48D0-90BB-9F9039DE9849}" name="option2" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{A3F2BD9D-835E-492D-AF60-1777FDBFC4A3}" name="option3" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{2B52C26E-7952-4BDC-BA0C-415990928F70}" name="option4" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{6B8845CA-AD71-4B12-BE16-31F17CE35C2B}" name="correct" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{81BCF052-D165-4872-A5EE-1654D4C54DA4}" name="explanation" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{AC8E2E79-B61E-4526-B873-A7FAFED87C57}" name="Comments ZF" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{297BBB0E-9520-4E2B-9EFD-487273B84694}" name="Questions6" displayName="Questions6" ref="A1:J11" headerRowDxfId="28" dataDxfId="26" totalsRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{297BBB0E-9520-4E2B-9EFD-487273B84694}" name="Questions6" displayName="Questions6" ref="A1:J11" headerRowDxfId="39" dataDxfId="38" totalsRowDxfId="37">
   <autoFilter ref="A1:J11" xr:uid="{297BBB0E-9520-4E2B-9EFD-487273B84694}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{269689A4-8524-44F7-AB3C-C986EB964566}" name="type" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{AF0F837B-05E2-458B-9355-35D83FEAB50A}" name="question" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{11FB13A4-56AF-49AD-8C21-3974B4BB8B4F}" name="note" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{14AF9A0A-7D77-4E95-9C18-94C7DF2E387E}" name="option1" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{E7EDDCA7-44EF-4840-B137-D661FB49CD80}" name="option2" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{2253FC1B-6F77-4E85-9B3E-634EDF3C1A62}" name="option3" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{767FE039-9A76-4E8C-B8F2-9503D2A65155}" name="option4" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{CF7A521D-AF97-43D9-9D4F-D3AC3AC4E1E4}" name="correct" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{52FB7FB7-77DB-4D37-8DEE-4F22E39E8CFC}" name="explanation" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{E0AD96DA-8695-4CBF-A6CF-451B886B7CEC}" name="Comments ZF" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{269689A4-8524-44F7-AB3C-C986EB964566}" name="type" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{AF0F837B-05E2-458B-9355-35D83FEAB50A}" name="question" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{11FB13A4-56AF-49AD-8C21-3974B4BB8B4F}" name="note" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{14AF9A0A-7D77-4E95-9C18-94C7DF2E387E}" name="option1" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{E7EDDCA7-44EF-4840-B137-D661FB49CD80}" name="option2" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{2253FC1B-6F77-4E85-9B3E-634EDF3C1A62}" name="option3" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{767FE039-9A76-4E8C-B8F2-9503D2A65155}" name="option4" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{CF7A521D-AF97-43D9-9D4F-D3AC3AC4E1E4}" name="correct" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{52FB7FB7-77DB-4D37-8DEE-4F22E39E8CFC}" name="explanation" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{E0AD96DA-8695-4CBF-A6CF-451B886B7CEC}" name="Comments ZF" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9B39E198-42CF-40FA-B1F2-1D2585A3AA50}" name="Questions8" displayName="Questions8" ref="A1:J11" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9B39E198-42CF-40FA-B1F2-1D2585A3AA50}" name="Questions8" displayName="Questions8" ref="A1:J11" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
   <autoFilter ref="A1:J11" xr:uid="{9B39E198-42CF-40FA-B1F2-1D2585A3AA50}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{26652740-DD74-48B9-AA4D-F6CC506CEED4}" name="type" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{818B5848-9855-4A56-BD48-CB7BFA95664A}" name="question" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{11EC098A-B461-4B44-BEF8-951C4C041A18}" name="note" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{B9F3AE6E-F720-482D-A532-7E554F9E9167}" name="option1" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{7661A812-1B4B-47B8-8747-65EF9D25A215}" name="option2" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{1414C680-8CFF-4D00-B0BB-532BD863B581}" name="option3" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{C6B17D26-6E8A-4DCE-AC14-20F4A0BFFFDD}" name="option4" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{F39AEDA6-7ACE-40EF-9C85-646EFE3213BC}" name="correct" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{4355FDC4-615B-497D-8859-BC903E8081F1}" name="explanation" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{2A94411C-5024-44FF-91EC-1FB4D53F6A14}" name="Comments ZF" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{26652740-DD74-48B9-AA4D-F6CC506CEED4}" name="type" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{818B5848-9855-4A56-BD48-CB7BFA95664A}" name="question" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{11EC098A-B461-4B44-BEF8-951C4C041A18}" name="note" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{B9F3AE6E-F720-482D-A532-7E554F9E9167}" name="option1" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{7661A812-1B4B-47B8-8747-65EF9D25A215}" name="option2" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{1414C680-8CFF-4D00-B0BB-532BD863B581}" name="option3" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{C6B17D26-6E8A-4DCE-AC14-20F4A0BFFFDD}" name="option4" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{F39AEDA6-7ACE-40EF-9C85-646EFE3213BC}" name="correct" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{4355FDC4-615B-497D-8859-BC903E8081F1}" name="explanation" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{2A94411C-5024-44FF-91EC-1FB4D53F6A14}" name="Comments ZF" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{97115BCE-407F-4CCB-887E-3757D56D1785}" name="Questions7" displayName="Questions7" ref="A1:J11" headerRowDxfId="15" dataDxfId="13" totalsRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{97115BCE-407F-4CCB-887E-3757D56D1785}" name="Questions7" displayName="Questions7" ref="A1:J11" headerRowDxfId="13" dataDxfId="12" totalsRowDxfId="11">
   <autoFilter ref="A1:J11" xr:uid="{97115BCE-407F-4CCB-887E-3757D56D1785}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1E22D3F9-75E8-41A3-980E-5ADABF66F80D}" name="type" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{899347D3-2BCF-4DF0-85D9-0DB60EB93C6C}" name="question" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{BEF59DFC-561B-4878-8C53-7411F154A7B6}" name="note" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{DEB3D9B0-38FA-4069-AEBB-1EE9FF2FFB66}" name="option1" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{BF79F551-0174-4D29-85EA-F83D231367C1}" name="option2" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{CDB6BE02-8325-4A14-B524-49D4166C7EA3}" name="option3" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00DFFE8A-9149-4143-9721-A108E7AFDE17}" name="option4" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{D102CC30-F7A0-46C9-B87F-E793BB482785}" name="correct" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{FB9D77C4-6187-4AC4-BCFA-1424CAB8EA81}" name="explanation" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{A7E8D84B-0DB0-46E7-B1F5-B5C2695512DE}" name="Comments ZF" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{1E22D3F9-75E8-41A3-980E-5ADABF66F80D}" name="type" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{899347D3-2BCF-4DF0-85D9-0DB60EB93C6C}" name="question" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BEF59DFC-561B-4878-8C53-7411F154A7B6}" name="note" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{DEB3D9B0-38FA-4069-AEBB-1EE9FF2FFB66}" name="option1" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{BF79F551-0174-4D29-85EA-F83D231367C1}" name="option2" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{CDB6BE02-8325-4A14-B524-49D4166C7EA3}" name="option3" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00DFFE8A-9149-4143-9721-A108E7AFDE17}" name="option4" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{D102CC30-F7A0-46C9-B87F-E793BB482785}" name="correct" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{FB9D77C4-6187-4AC4-BCFA-1424CAB8EA81}" name="explanation" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{A7E8D84B-0DB0-46E7-B1F5-B5C2695512DE}" name="Comments ZF" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2116,8 +2178,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -2126,9 +2188,10 @@
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="75" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2159,8 +2222,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2190,7 +2256,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2219,8 +2285,11 @@
         <v>24</v>
       </c>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K3" s="6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2249,8 +2318,11 @@
         <v>30</v>
       </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K4" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2280,7 +2352,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2310,7 +2382,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2340,7 +2412,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2370,7 +2442,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2400,7 +2472,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2430,7 +2502,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2470,19 +2542,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52972993-27BC-4569-9A65-F27DD5C5913E}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="37.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="7" width="37.28515625" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="54.54296875" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2513,8 +2586,11 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2544,7 +2620,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2573,8 +2649,11 @@
         <v>87</v>
       </c>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K3" s="6" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2603,8 +2682,11 @@
         <v>93</v>
       </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K4" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2634,7 +2716,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2664,7 +2746,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2694,7 +2776,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2724,7 +2806,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -2754,7 +2836,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -2784,7 +2866,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2824,19 +2906,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A86264-DF27-49EA-A41C-846F782DB5F5}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="37.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="7" width="37.28515625" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="54.54296875" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2867,8 +2950,11 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2898,7 +2984,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2927,8 +3013,11 @@
         <v>149</v>
       </c>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K3" s="6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2957,8 +3046,11 @@
         <v>155</v>
       </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K4" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2988,7 +3080,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3018,7 +3110,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3048,7 +3140,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3078,7 +3170,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3108,7 +3200,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3138,7 +3230,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3178,19 +3270,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA0415C7-5D8F-4D25-9E10-1A5F259EDF1E}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="37.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="7" width="37.28515625" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="54.54296875" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3221,8 +3314,11 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3252,7 +3348,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3281,8 +3377,11 @@
         <v>211</v>
       </c>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K3" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3311,8 +3410,11 @@
         <v>217</v>
       </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K4" s="6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3342,7 +3444,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3372,7 +3474,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3402,7 +3504,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3432,7 +3534,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3462,7 +3564,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3492,7 +3594,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3532,19 +3634,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8918212-4945-42E0-A676-543ADBE07649}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="37.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="7" width="37.28515625" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="54.54296875" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3575,8 +3678,11 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3606,7 +3712,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3635,8 +3741,11 @@
         <v>273</v>
       </c>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K3" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3665,8 +3774,11 @@
         <v>279</v>
       </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K4" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3696,7 +3808,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -3726,7 +3838,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -3756,7 +3868,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -3786,7 +3898,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -3816,7 +3928,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -3846,7 +3958,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3886,19 +3998,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1854560F-3E42-4A84-AEBB-36CF0A1A6CF9}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="37.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="7" width="37.28515625" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="54.54296875" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3929,8 +4042,11 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -3960,7 +4076,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3989,8 +4105,11 @@
         <v>397</v>
       </c>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K3" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4019,8 +4138,11 @@
         <v>403</v>
       </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K4" s="6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -4050,7 +4172,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -4080,7 +4202,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -4110,7 +4232,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4140,7 +4262,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -4170,7 +4292,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -4200,7 +4322,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -4240,19 +4362,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB51948-4E76-4442-9DD6-09AB7002F07E}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20.90625" customWidth="1"/>
-    <col min="4" max="7" width="37.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="7" width="37.28515625" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="54.54296875" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4283,8 +4406,11 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K1" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -4314,7 +4440,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -4343,8 +4469,11 @@
         <v>335</v>
       </c>
       <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="K3" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4373,8 +4502,11 @@
         <v>341</v>
       </c>
       <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K4" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -4404,7 +4536,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -4434,7 +4566,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -4464,7 +4596,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -4494,7 +4626,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -4524,7 +4656,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -4554,7 +4686,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -4593,25 +4725,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006B71C29808C7F3499BFFC3671560B6FA" ma:contentTypeVersion="8" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e4f9e1976b194f932bebfa03c600f49f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2aad7df3-4ab7-4daa-980d-cf7206357ce9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d33a1b74cd678b812bcd025038ca576" ns2:_="">
     <xsd:import namespace="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
@@ -4775,26 +4888,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85235A32-E589-4A54-94A9-1CBE61A18806}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2aad7df3-4ab7-4daa-980d-cf7206357ce9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BEDAAEC-57CA-40AB-894C-EC0C8327F96C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4306851-3F47-469C-9956-A73B86D84FEF}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BDBC2CF-1AC0-4754-A141-F5BE55764874}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -4809,4 +4923,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85235A32-E589-4A54-94A9-1CBE61A18806}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BEDAAEC-57CA-40AB-894C-EC0C8327F96C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>